--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/57.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/57.xlsx
@@ -426,13 +426,13 @@
         <v>-4.256320808938823</v>
       </c>
       <c r="E2">
-        <v>-5.282317567012821</v>
+        <v>-4.712119290811016</v>
       </c>
       <c r="F2">
-        <v>-7.289189247019662</v>
+        <v>-7.07143918588223</v>
       </c>
       <c r="G2">
-        <v>-1.403258641126908</v>
+        <v>-1.33616050413696</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.152664128588049</v>
       </c>
       <c r="E3">
-        <v>-5.165845215535539</v>
+        <v>-6.015477508854651</v>
       </c>
       <c r="F3">
-        <v>-7.790775833439898</v>
+        <v>-6.937724123956325</v>
       </c>
       <c r="G3">
-        <v>-1.305872322998168</v>
+        <v>-1.02200959573336</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.114211577947914</v>
       </c>
       <c r="E4">
-        <v>-5.278522705794393</v>
+        <v>-6.164206180688569</v>
       </c>
       <c r="F4">
-        <v>-7.85070524491252</v>
+        <v>-7.14319729683727</v>
       </c>
       <c r="G4">
-        <v>-1.46353043321488</v>
+        <v>-1.033030401833594</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.322524223315594</v>
       </c>
       <c r="E5">
-        <v>-5.994904651437805</v>
+        <v>-6.408784533368838</v>
       </c>
       <c r="F5">
-        <v>-7.705605713013479</v>
+        <v>-7.111591673809325</v>
       </c>
       <c r="G5">
-        <v>-1.124418011445175</v>
+        <v>-1.083790996587239</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.7638247688012192</v>
       </c>
       <c r="E6">
-        <v>-6.83749516767499</v>
+        <v>-7.54130606947311</v>
       </c>
       <c r="F6">
-        <v>-7.575164963067746</v>
+        <v>-7.316368016087476</v>
       </c>
       <c r="G6">
-        <v>-0.8064864600357271</v>
+        <v>-1.692285819432979</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.4582602372580675</v>
       </c>
       <c r="E7">
-        <v>-8.4035592198516</v>
+        <v>-8.053698374967002</v>
       </c>
       <c r="F7">
-        <v>-7.746987948583912</v>
+        <v>-6.951082683353057</v>
       </c>
       <c r="G7">
-        <v>-1.594177802376678</v>
+        <v>-1.763830019082169</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.3805145908396478</v>
       </c>
       <c r="E8">
-        <v>-8.560923691618145</v>
+        <v>-8.86893690819786</v>
       </c>
       <c r="F8">
-        <v>-7.645867929956625</v>
+        <v>-6.664110420357683</v>
       </c>
       <c r="G8">
-        <v>-0.424363430619811</v>
+        <v>-2.131770671407847</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.5047588753197875</v>
       </c>
       <c r="E9">
-        <v>-9.940591225165035</v>
+        <v>-9.623430491089826</v>
       </c>
       <c r="F9">
-        <v>-7.849528551417349</v>
+        <v>-6.989189419163883</v>
       </c>
       <c r="G9">
-        <v>-1.734290021235252</v>
+        <v>-2.402093267417036</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.7741313414990447</v>
       </c>
       <c r="E10">
-        <v>-10.90841216161033</v>
+        <v>-10.50913660835404</v>
       </c>
       <c r="F10">
-        <v>-7.602886151411598</v>
+        <v>-6.950499879576176</v>
       </c>
       <c r="G10">
-        <v>-2.10863988972496</v>
+        <v>-1.850877503491765</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.135381263278287</v>
       </c>
       <c r="E11">
-        <v>-11.04686572592085</v>
+        <v>-11.63387822611313</v>
       </c>
       <c r="F11">
-        <v>-7.116134138301284</v>
+        <v>-6.89388793606992</v>
       </c>
       <c r="G11">
-        <v>-1.215554019595771</v>
+        <v>-2.038575503931824</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.526753912285064</v>
       </c>
       <c r="E12">
-        <v>-11.67906786823568</v>
+        <v>-12.47184064191448</v>
       </c>
       <c r="F12">
-        <v>-7.318266879480087</v>
+        <v>-6.610111987538381</v>
       </c>
       <c r="G12">
-        <v>-1.660004689879546</v>
+        <v>-1.921544408573048</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.889831053881883</v>
       </c>
       <c r="E13">
-        <v>-12.87757379910571</v>
+        <v>-13.11794067095885</v>
       </c>
       <c r="F13">
-        <v>-7.011072275650467</v>
+        <v>-6.414087204148948</v>
       </c>
       <c r="G13">
-        <v>-1.944777817167654</v>
+        <v>-2.041535131643932</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.177804730179572</v>
       </c>
       <c r="E14">
-        <v>-12.87881007250981</v>
+        <v>-14.83407835174965</v>
       </c>
       <c r="F14">
-        <v>-7.029313400384499</v>
+        <v>-6.398459194175391</v>
       </c>
       <c r="G14">
-        <v>-0.9861530769975136</v>
+        <v>-2.152968094495801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.357397275749203</v>
       </c>
       <c r="E15">
-        <v>-14.1317844887441</v>
+        <v>-13.94330034359685</v>
       </c>
       <c r="F15">
-        <v>-7.064129195303041</v>
+        <v>-5.966241302410277</v>
       </c>
       <c r="G15">
-        <v>-1.06811556345879</v>
+        <v>-0.9487571545859064</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.412141251421789</v>
       </c>
       <c r="E16">
-        <v>-14.69096498768525</v>
+        <v>-14.1523256468429</v>
       </c>
       <c r="F16">
-        <v>-6.29886824360946</v>
+        <v>-5.906798484580173</v>
       </c>
       <c r="G16">
-        <v>-0.9916518931382431</v>
+        <v>-0.5737220031695699</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.347475794463243</v>
       </c>
       <c r="E17">
-        <v>-15.61954669685408</v>
+        <v>-16.32967934836691</v>
       </c>
       <c r="F17">
-        <v>-6.406327837016252</v>
+        <v>-5.882357151187196</v>
       </c>
       <c r="G17">
-        <v>-0.7126920838170958</v>
+        <v>0.2544010318424997</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.189043491619065</v>
       </c>
       <c r="E18">
-        <v>-15.66606771033488</v>
+        <v>-15.80503752068227</v>
       </c>
       <c r="F18">
-        <v>-6.259405459608541</v>
+        <v>-5.30564430725626</v>
       </c>
       <c r="G18">
-        <v>-0.7435629209707996</v>
+        <v>-0.563737397823128</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.975121411068968</v>
       </c>
       <c r="E19">
-        <v>-17.60091710027414</v>
+        <v>-18.54665266898403</v>
       </c>
       <c r="F19">
-        <v>-5.941589336130547</v>
+        <v>-5.376497726207105</v>
       </c>
       <c r="G19">
-        <v>-0.1575864288831817</v>
+        <v>0.5431799192331254</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.75032593119319</v>
       </c>
       <c r="E20">
-        <v>-18.03279313791166</v>
+        <v>-18.10072024802671</v>
       </c>
       <c r="F20">
-        <v>-5.874952534179559</v>
+        <v>-4.708743964021216</v>
       </c>
       <c r="G20">
-        <v>0.3347810775360042</v>
+        <v>0.1995386711656976</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.558964508133434</v>
       </c>
       <c r="E21">
-        <v>-18.64903240934945</v>
+        <v>-19.13141451759451</v>
       </c>
       <c r="F21">
-        <v>-5.434248354266562</v>
+        <v>-5.011938126708436</v>
       </c>
       <c r="G21">
-        <v>0.6131946468431717</v>
+        <v>0.2139130598972131</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.434458659173486</v>
       </c>
       <c r="E22">
-        <v>-19.6419184494272</v>
+        <v>-20.18055779026955</v>
       </c>
       <c r="F22">
-        <v>-5.364553416192861</v>
+        <v>-4.722488947661315</v>
       </c>
       <c r="G22">
-        <v>0.4820242114861688</v>
+        <v>0.6641174583282411</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.398052410484959</v>
       </c>
       <c r="E23">
-        <v>-19.8144850084375</v>
+        <v>-21.72418325373815</v>
       </c>
       <c r="F23">
-        <v>-4.986603583179152</v>
+        <v>-4.429972922108945</v>
       </c>
       <c r="G23">
-        <v>0.2461014941755469</v>
+        <v>-0.1702790604807474</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.457740937237728</v>
       </c>
       <c r="E24">
-        <v>-20.67883484228154</v>
+        <v>-20.84574533725625</v>
       </c>
       <c r="F24">
-        <v>-4.804913713883319</v>
+        <v>-4.5638855513478</v>
       </c>
       <c r="G24">
-        <v>-0.6379399655403524</v>
+        <v>0.4577512915922324</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.605475558597767</v>
       </c>
       <c r="E25">
-        <v>-20.5858879132741</v>
+        <v>-21.39460997240792</v>
       </c>
       <c r="F25">
-        <v>-4.684069825858669</v>
+        <v>-3.860413677798049</v>
       </c>
       <c r="G25">
-        <v>-0.7691335747161303</v>
+        <v>-0.5777575581819415</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.824448626203957</v>
       </c>
       <c r="E26">
-        <v>-20.29952533092506</v>
+        <v>-21.06959686440341</v>
       </c>
       <c r="F26">
-        <v>-4.828906858502227</v>
+        <v>-4.641807049799253</v>
       </c>
       <c r="G26">
-        <v>-1.049910873538337</v>
+        <v>-0.5699181863449473</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.090216270164459</v>
       </c>
       <c r="E27">
-        <v>-20.38669845557272</v>
+        <v>-22.62123319839158</v>
       </c>
       <c r="F27">
-        <v>-4.606873664716489</v>
+        <v>-4.302264460793824</v>
       </c>
       <c r="G27">
-        <v>-0.9690971463791885</v>
+        <v>-0.2287830212507478</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.371584843720298</v>
       </c>
       <c r="E28">
-        <v>-20.83053419306449</v>
+        <v>-21.95035788805125</v>
       </c>
       <c r="F28">
-        <v>-4.883388717552217</v>
+        <v>-4.191970429724874</v>
       </c>
       <c r="G28">
-        <v>-1.603007027329914</v>
+        <v>-0.9772775044067276</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.639925489978721</v>
       </c>
       <c r="E29">
-        <v>-20.98326603592119</v>
+        <v>-21.32415144532258</v>
       </c>
       <c r="F29">
-        <v>-4.667233448271633</v>
+        <v>-4.338867863764418</v>
       </c>
       <c r="G29">
-        <v>-1.292186527738821</v>
+        <v>-1.21233285878606</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.869005903390169</v>
       </c>
       <c r="E30">
-        <v>-21.26618244955039</v>
+        <v>-21.62870943623444</v>
       </c>
       <c r="F30">
-        <v>-4.69715440413203</v>
+        <v>-4.590590792346898</v>
       </c>
       <c r="G30">
-        <v>-1.877815412544815</v>
+        <v>-0.8334011952700018</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.03691819354479</v>
       </c>
       <c r="E31">
-        <v>-21.64697730038138</v>
+        <v>-21.74531764193195</v>
       </c>
       <c r="F31">
-        <v>-5.151264654619222</v>
+        <v>-4.218664584782563</v>
       </c>
       <c r="G31">
-        <v>-1.730694768779604</v>
+        <v>-0.7084148589803574</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.131983372654054</v>
       </c>
       <c r="E32">
-        <v>-20.35791094630595</v>
+        <v>-20.66735063219809</v>
       </c>
       <c r="F32">
-        <v>-4.671047803968968</v>
+        <v>-4.690050691248326</v>
       </c>
       <c r="G32">
-        <v>-2.088965317585071</v>
+        <v>-0.7637704909425109</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.15082590942245</v>
       </c>
       <c r="E33">
-        <v>-19.96114869612392</v>
+        <v>-21.85798607524279</v>
       </c>
       <c r="F33">
-        <v>-4.939559598961023</v>
+        <v>-4.601764629433282</v>
       </c>
       <c r="G33">
-        <v>-1.339176411123236</v>
+        <v>-0.6433659496792179</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.097147792827245</v>
       </c>
       <c r="E34">
-        <v>-21.21773683461633</v>
+        <v>-20.8232795777042</v>
       </c>
       <c r="F34">
-        <v>-4.974288685980695</v>
+        <v>-4.307301437457879</v>
       </c>
       <c r="G34">
-        <v>-0.9150889064515183</v>
+        <v>-0.9444666875670109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.98326716596759</v>
       </c>
       <c r="E35">
-        <v>-20.12587646662693</v>
+        <v>-19.88702663356637</v>
       </c>
       <c r="F35">
-        <v>-4.854543098008403</v>
+        <v>-4.607891195767159</v>
       </c>
       <c r="G35">
-        <v>-0.747254179247087</v>
+        <v>0.001756749013019087</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.824670640880478</v>
       </c>
       <c r="E36">
-        <v>-19.03435573418811</v>
+        <v>-20.86610535639474</v>
       </c>
       <c r="F36">
-        <v>-4.697830646557922</v>
+        <v>-4.121801171729499</v>
       </c>
       <c r="G36">
-        <v>-0.6077477902221992</v>
+        <v>-1.343675442511105</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.635587398714422</v>
       </c>
       <c r="E37">
-        <v>-20.35261263171698</v>
+        <v>-20.81305881186889</v>
       </c>
       <c r="F37">
-        <v>-5.084454436870494</v>
+        <v>-4.387046573270958</v>
       </c>
       <c r="G37">
-        <v>-0.2757000726332991</v>
+        <v>0.03067767484409218</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.429744460627245</v>
       </c>
       <c r="E38">
-        <v>-18.312249797399</v>
+        <v>-19.75460499663407</v>
       </c>
       <c r="F38">
-        <v>-4.963769711290346</v>
+        <v>-4.256333821834248</v>
       </c>
       <c r="G38">
-        <v>0.05590072130779935</v>
+        <v>-0.8742069795870585</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.216121101482577</v>
       </c>
       <c r="E39">
-        <v>-18.76065929363852</v>
+        <v>-20.31858114954934</v>
       </c>
       <c r="F39">
-        <v>-5.071357188949809</v>
+        <v>-4.269316251076064</v>
       </c>
       <c r="G39">
-        <v>-0.4482026690481029</v>
+        <v>1.020544033268334</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.998478735060212</v>
       </c>
       <c r="E40">
-        <v>-18.42257700964787</v>
+        <v>-19.02554332376918</v>
       </c>
       <c r="F40">
-        <v>-4.607500020406046</v>
+        <v>-3.849144818356739</v>
       </c>
       <c r="G40">
-        <v>0.3466626254764484</v>
+        <v>-0.09219984393703648</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.779879604768936</v>
       </c>
       <c r="E41">
-        <v>-18.12794543376083</v>
+        <v>-18.6035438879424</v>
       </c>
       <c r="F41">
-        <v>-4.859707562998651</v>
+        <v>-4.301906543256934</v>
       </c>
       <c r="G41">
-        <v>0.3281301915476083</v>
+        <v>0.2864504232081841</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.561001666333965</v>
       </c>
       <c r="E42">
-        <v>-18.35911497490438</v>
+        <v>-18.89733316766402</v>
       </c>
       <c r="F42">
-        <v>-4.926590631219489</v>
+        <v>-4.492754983861754</v>
       </c>
       <c r="G42">
-        <v>-0.3595396384153419</v>
+        <v>0.4331671804176045</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.341930362716874</v>
       </c>
       <c r="E43">
-        <v>-18.14218748451495</v>
+        <v>-17.39464963769876</v>
       </c>
       <c r="F43">
-        <v>-4.679785901357405</v>
+        <v>-3.913886716179904</v>
       </c>
       <c r="G43">
-        <v>-0.1102787331269964</v>
+        <v>0.7571470985273008</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.12624385168861</v>
       </c>
       <c r="E44">
-        <v>-17.10712776600376</v>
+        <v>-15.85349672103835</v>
       </c>
       <c r="F44">
-        <v>-4.709647468245974</v>
+        <v>-4.326824572130459</v>
       </c>
       <c r="G44">
-        <v>0.663236853214795</v>
+        <v>0.4745754840228086</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.9173785470792405</v>
       </c>
       <c r="E45">
-        <v>-17.25966035600412</v>
+        <v>-16.1248066557859</v>
       </c>
       <c r="F45">
-        <v>-4.931199215433418</v>
+        <v>-4.50672643744776</v>
       </c>
       <c r="G45">
-        <v>0.6726156287275502</v>
+        <v>0.08912866688546425</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7191143697321266</v>
       </c>
       <c r="E46">
-        <v>-17.38064759606705</v>
+        <v>-16.29254133303001</v>
       </c>
       <c r="F46">
-        <v>-4.702173960031016</v>
+        <v>-4.242694154637526</v>
       </c>
       <c r="G46">
-        <v>-0.3113745113644854</v>
+        <v>0.3279249377241735</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.5375583901910135</v>
       </c>
       <c r="E47">
-        <v>-16.63291955334254</v>
+        <v>-16.0603981699748</v>
       </c>
       <c r="F47">
-        <v>-5.124245839848867</v>
+        <v>-4.948358669027204</v>
       </c>
       <c r="G47">
-        <v>0.7654996049228819</v>
+        <v>0.6618133186329084</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3777128288621996</v>
       </c>
       <c r="E48">
-        <v>-16.37416254854426</v>
+        <v>-16.11014345694906</v>
       </c>
       <c r="F48">
-        <v>-5.062608005619964</v>
+        <v>-4.23009419037429</v>
       </c>
       <c r="G48">
-        <v>0.2454493167043104</v>
+        <v>0.2971401747544907</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2437778159799471</v>
       </c>
       <c r="E49">
-        <v>-16.10610405813422</v>
+        <v>-15.79569980727845</v>
       </c>
       <c r="F49">
-        <v>-5.083569937116721</v>
+        <v>-4.655574997175125</v>
       </c>
       <c r="G49">
-        <v>0.04117872529466038</v>
+        <v>-0.06217650644138608</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.1408457517507753</v>
       </c>
       <c r="E50">
-        <v>-15.94436055200226</v>
+        <v>-15.23626571379288</v>
       </c>
       <c r="F50">
-        <v>-5.175097053087712</v>
+        <v>-4.520446081793212</v>
       </c>
       <c r="G50">
-        <v>-0.2165969031206906</v>
+        <v>0.319605536783985</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.07250236392909583</v>
       </c>
       <c r="E51">
-        <v>-14.90412931617431</v>
+        <v>-15.65323854347115</v>
       </c>
       <c r="F51">
-        <v>-5.208475238961515</v>
+        <v>-4.665832660389427</v>
       </c>
       <c r="G51">
-        <v>-0.2550952371968752</v>
+        <v>0.0662461761180218</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.04050272130525406</v>
       </c>
       <c r="E52">
-        <v>-15.07681814398281</v>
+        <v>-13.81382674324354</v>
       </c>
       <c r="F52">
-        <v>-5.046328300662204</v>
+        <v>-4.28923293666863</v>
       </c>
       <c r="G52">
-        <v>0.1029899210583927</v>
+        <v>-0.2226651330941747</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.0468128064455385</v>
       </c>
       <c r="E53">
-        <v>-16.11245297869297</v>
+        <v>-14.80723355783218</v>
       </c>
       <c r="F53">
-        <v>-5.318345628698084</v>
+        <v>-4.766325927400679</v>
       </c>
       <c r="G53">
-        <v>0.1268986809430092</v>
+        <v>0.4373119834327721</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.09140515598345623</v>
       </c>
       <c r="E54">
-        <v>-14.38442805363203</v>
+        <v>-14.30832704793313</v>
       </c>
       <c r="F54">
-        <v>-5.303981416045048</v>
+        <v>-4.56667762487672</v>
       </c>
       <c r="G54">
-        <v>0.4716456512205536</v>
+        <v>0.02683082092745906</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.1726764721879434</v>
       </c>
       <c r="E55">
-        <v>-15.29293503752487</v>
+        <v>-13.31253372754245</v>
       </c>
       <c r="F55">
-        <v>-5.838688044274869</v>
+        <v>-4.993141121198086</v>
       </c>
       <c r="G55">
-        <v>0.0794254579098604</v>
+        <v>0.5634834950254756</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.2901476910674309</v>
       </c>
       <c r="E56">
-        <v>-13.43671807025479</v>
+        <v>-12.66379359815161</v>
       </c>
       <c r="F56">
-        <v>-5.186555957238874</v>
+        <v>-5.010435189794684</v>
       </c>
       <c r="G56">
-        <v>-0.1115466720685373</v>
+        <v>0.5481821535429642</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.4418936289881568</v>
       </c>
       <c r="E57">
-        <v>-14.13483668022527</v>
+        <v>-12.75722507387787</v>
       </c>
       <c r="F57">
-        <v>-5.676969498425684</v>
+        <v>-5.304883336563891</v>
       </c>
       <c r="G57">
-        <v>-0.2475140879119442</v>
+        <v>0.4068218590160845</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6239891601829831</v>
       </c>
       <c r="E58">
-        <v>-14.77366850848733</v>
+        <v>-12.66488043191345</v>
       </c>
       <c r="F58">
-        <v>-5.71833352137809</v>
+        <v>-4.410518678643687</v>
       </c>
       <c r="G58">
-        <v>0.2460187305370651</v>
+        <v>-0.5731658315189724</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8346882978507859</v>
       </c>
       <c r="E59">
-        <v>-13.74771555120556</v>
+        <v>-11.65412050492742</v>
       </c>
       <c r="F59">
-        <v>-5.435323690583146</v>
+        <v>-4.966847643737002</v>
       </c>
       <c r="G59">
-        <v>0.7924408245214709</v>
+        <v>0.1611065480002984</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.072064233139072</v>
       </c>
       <c r="E60">
-        <v>-13.92941604228933</v>
+        <v>-12.40548491228009</v>
       </c>
       <c r="F60">
-        <v>-5.21082070742228</v>
+        <v>-4.701040818448519</v>
       </c>
       <c r="G60">
-        <v>-0.2290942125314393</v>
+        <v>-0.7409740743590896</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.331351434927799</v>
       </c>
       <c r="E61">
-        <v>-13.28406773993023</v>
+        <v>-13.24525418921049</v>
       </c>
       <c r="F61">
-        <v>-5.188988529524989</v>
+        <v>-4.997705361646382</v>
       </c>
       <c r="G61">
-        <v>0.6934886183526551</v>
+        <v>0.4964118423998413</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.607730208039819</v>
       </c>
       <c r="E62">
-        <v>-13.78552830916961</v>
+        <v>-11.81523455317232</v>
       </c>
       <c r="F62">
-        <v>-5.201411910578654</v>
+        <v>-4.676751520823424</v>
       </c>
       <c r="G62">
-        <v>0.1435209300956899</v>
+        <v>0.2046931905703429</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.894294783401606</v>
       </c>
       <c r="E63">
-        <v>-12.48750916198102</v>
+        <v>-10.88196134493153</v>
       </c>
       <c r="F63">
-        <v>-5.406793228516504</v>
+        <v>-4.956205931838207</v>
       </c>
       <c r="G63">
-        <v>0.6743768389544426</v>
+        <v>-0.4628849385147706</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.182099227541479</v>
       </c>
       <c r="E64">
-        <v>-13.01054338139294</v>
+        <v>-12.84348344677597</v>
       </c>
       <c r="F64">
-        <v>-5.310351081236945</v>
+        <v>-5.119786123990989</v>
       </c>
       <c r="G64">
-        <v>-0.6391747990265005</v>
+        <v>-1.006887023709969</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.463435717398501</v>
       </c>
       <c r="E65">
-        <v>-13.82719932698819</v>
+        <v>-11.96047630002033</v>
       </c>
       <c r="F65">
-        <v>-5.181415247837358</v>
+        <v>-4.727879090744513</v>
       </c>
       <c r="G65">
-        <v>-0.3068456850667624</v>
+        <v>-1.54615502878401</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.72835383116422</v>
       </c>
       <c r="E66">
-        <v>-13.64183077195822</v>
+        <v>-12.12261378339096</v>
       </c>
       <c r="F66">
-        <v>-4.953773359552092</v>
+        <v>-4.58552372527045</v>
       </c>
       <c r="G66">
-        <v>-0.7379151302808029</v>
+        <v>-0.7103780124851452</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.964865799641953</v>
       </c>
       <c r="E67">
-        <v>-12.43978357441418</v>
+        <v>-12.5304753233658</v>
       </c>
       <c r="F67">
-        <v>-5.278733184488154</v>
+        <v>-4.995340888714631</v>
       </c>
       <c r="G67">
-        <v>-0.5120001921353979</v>
+        <v>-1.417255627666947</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.163132419639689</v>
       </c>
       <c r="E68">
-        <v>-13.20097024188948</v>
+        <v>-12.39480224209599</v>
       </c>
       <c r="F68">
-        <v>-5.419343306043404</v>
+        <v>-4.729582366456568</v>
       </c>
       <c r="G68">
-        <v>-1.118564966931743</v>
+        <v>-0.9103448946937427</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.313139342434451</v>
       </c>
       <c r="E69">
-        <v>-13.19776408229205</v>
+        <v>-10.35695271085227</v>
       </c>
       <c r="F69">
-        <v>-5.477841443294948</v>
+        <v>-4.810375123732712</v>
       </c>
       <c r="G69">
-        <v>-0.6353544294741816</v>
+        <v>-2.123649903200015</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.406029120967967</v>
       </c>
       <c r="E70">
-        <v>-12.36610530230938</v>
+        <v>-11.06298256491415</v>
       </c>
       <c r="F70">
-        <v>-5.357263617864093</v>
+        <v>-4.733867082810789</v>
       </c>
       <c r="G70">
-        <v>-1.092160055710516</v>
+        <v>-1.258528211241051</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.438197796673935</v>
       </c>
       <c r="E71">
-        <v>-13.45673845384271</v>
+        <v>-10.88725965952051</v>
       </c>
       <c r="F71">
-        <v>-5.641304441209988</v>
+        <v>-4.618961300116081</v>
       </c>
       <c r="G71">
-        <v>-1.811299931569778</v>
+        <v>-2.069966096735194</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.409419601809581</v>
       </c>
       <c r="E72">
-        <v>-13.86978962503033</v>
+        <v>-12.47981981311599</v>
       </c>
       <c r="F72">
-        <v>-4.914611479675106</v>
+        <v>-4.696726011681903</v>
       </c>
       <c r="G72">
-        <v>-1.742619353812058</v>
+        <v>-2.149554922044812</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.323537085189882</v>
       </c>
       <c r="E73">
-        <v>-13.00700664319295</v>
+        <v>-11.50724850743665</v>
       </c>
       <c r="F73">
-        <v>-5.095947390698838</v>
+        <v>-4.710162172668492</v>
       </c>
       <c r="G73">
-        <v>-1.72212707692397</v>
+        <v>-1.44771926771932</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.189329984259606</v>
       </c>
       <c r="E74">
-        <v>-13.52381873931833</v>
+        <v>-12.7400078157007</v>
       </c>
       <c r="F74">
-        <v>-5.16230150114392</v>
+        <v>-4.971919461931197</v>
       </c>
       <c r="G74">
-        <v>-2.095788351941509</v>
+        <v>-1.524798699510171</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.01573858703383</v>
       </c>
       <c r="E75">
-        <v>-13.5175468028177</v>
+        <v>-12.70327736302449</v>
       </c>
       <c r="F75">
-        <v>-5.154453446479959</v>
+        <v>-5.022838774524407</v>
       </c>
       <c r="G75">
-        <v>-2.472591334675816</v>
+        <v>-2.191655129667724</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.812975656341275</v>
       </c>
       <c r="E76">
-        <v>-14.14147542312052</v>
+        <v>-12.37820991333189</v>
       </c>
       <c r="F76">
-        <v>-5.468903798961166</v>
+        <v>-4.960450263691585</v>
       </c>
       <c r="G76">
-        <v>-2.421009724628432</v>
+        <v>-1.153232999818991</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.593072982661046</v>
       </c>
       <c r="E77">
-        <v>-13.98304223148816</v>
+        <v>-13.36937513328673</v>
       </c>
       <c r="F77">
-        <v>-5.394243942842562</v>
+        <v>-5.187475298522787</v>
       </c>
       <c r="G77">
-        <v>-2.6886077416588</v>
+        <v>-2.445252849612515</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.365519613490774</v>
       </c>
       <c r="E78">
-        <v>-14.80670825484729</v>
+        <v>-12.51053645231002</v>
       </c>
       <c r="F78">
-        <v>-5.174012214535637</v>
+        <v>-4.777765035227898</v>
       </c>
       <c r="G78">
-        <v>-2.344671855038377</v>
+        <v>-2.417924296185831</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.139183721663552</v>
       </c>
       <c r="E79">
-        <v>-14.44882748249511</v>
+        <v>-13.3692981492286</v>
       </c>
       <c r="F79">
-        <v>-5.50972619449049</v>
+        <v>-4.863135494452619</v>
       </c>
       <c r="G79">
-        <v>-2.815980981282259</v>
+        <v>-1.49578176785846</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.923822430490517</v>
       </c>
       <c r="E80">
-        <v>-15.69387706921598</v>
+        <v>-14.05802923258118</v>
       </c>
       <c r="F80">
-        <v>-5.511371664936632</v>
+        <v>-4.908381180603767</v>
       </c>
       <c r="G80">
-        <v>-2.774612404223527</v>
+        <v>-2.281029927591428</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.725906812126816</v>
       </c>
       <c r="E81">
-        <v>-15.31473058292378</v>
+        <v>-15.37659406634257</v>
       </c>
       <c r="F81">
-        <v>-5.492664138810504</v>
+        <v>-5.310724043980032</v>
       </c>
       <c r="G81">
-        <v>-2.949402587605967</v>
+        <v>-2.290872179479681</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.55117288038813</v>
       </c>
       <c r="E82">
-        <v>-16.88944854892905</v>
+        <v>-16.18033480406795</v>
       </c>
       <c r="F82">
-        <v>-5.57494557964716</v>
+        <v>-5.624869533072515</v>
       </c>
       <c r="G82">
-        <v>-2.151660429007789</v>
+        <v>-3.261851875602381</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.406089463466573</v>
       </c>
       <c r="E83">
-        <v>-15.65316608788703</v>
+        <v>-16.20107068654907</v>
       </c>
       <c r="F83">
-        <v>-5.55877356669165</v>
+        <v>-5.789853680519335</v>
       </c>
       <c r="G83">
-        <v>-3.28461518673041</v>
+        <v>-2.826068213540418</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.293413312324004</v>
       </c>
       <c r="E84">
-        <v>-18.23707712887167</v>
+        <v>-17.22066113785006</v>
       </c>
       <c r="F84">
-        <v>-5.602060208625399</v>
+        <v>-5.676092125348531</v>
       </c>
       <c r="G84">
-        <v>-2.973082919848373</v>
+        <v>-3.080241968409042</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.215616899147306</v>
       </c>
       <c r="E85">
-        <v>-18.4082443894136</v>
+        <v>-17.72773248638494</v>
       </c>
       <c r="F85">
-        <v>-5.606693340281017</v>
+        <v>-5.734574425540922</v>
       </c>
       <c r="G85">
-        <v>-3.449738577138178</v>
+        <v>-2.466625731614049</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.175531239960353</v>
       </c>
       <c r="E86">
-        <v>-19.72082710901086</v>
+        <v>-19.49029155422837</v>
       </c>
       <c r="F86">
-        <v>-5.8650274492075</v>
+        <v>-5.560771411703977</v>
       </c>
       <c r="G86">
-        <v>-2.88388689138379</v>
+        <v>-2.850605977077497</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.171416135019258</v>
       </c>
       <c r="E87">
-        <v>-21.75970913232833</v>
+        <v>-20.48931367658653</v>
       </c>
       <c r="F87">
-        <v>-5.632839533091965</v>
+        <v>-5.21592182417591</v>
       </c>
       <c r="G87">
-        <v>-3.859064359250286</v>
+        <v>-3.036536146199584</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.199914338856497</v>
       </c>
       <c r="E88">
-        <v>-21.94246022938188</v>
+        <v>-22.0107224465735</v>
       </c>
       <c r="F88">
-        <v>-5.538061860729533</v>
+        <v>-5.662887185425597</v>
       </c>
       <c r="G88">
-        <v>-4.100161459238788</v>
+        <v>-3.424813479773005</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.257296394342478</v>
       </c>
       <c r="E89">
-        <v>-24.83630908839949</v>
+        <v>-23.74927607370227</v>
       </c>
       <c r="F89">
-        <v>-5.716066446360139</v>
+        <v>-5.510727096629048</v>
       </c>
       <c r="G89">
-        <v>-4.039035546401685</v>
+        <v>-3.540944106745099</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.335274469300166</v>
       </c>
       <c r="E90">
-        <v>-24.88292067136044</v>
+        <v>-24.03665303422903</v>
       </c>
       <c r="F90">
-        <v>-5.693931780632999</v>
+        <v>-5.545428468795199</v>
       </c>
       <c r="G90">
-        <v>-4.46027267136409</v>
+        <v>-3.560145270872872</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.424830978159092</v>
       </c>
       <c r="E91">
-        <v>-26.98454470205419</v>
+        <v>-25.79534478526991</v>
       </c>
       <c r="F91">
-        <v>-5.691002716542394</v>
+        <v>-5.805306690989235</v>
       </c>
       <c r="G91">
-        <v>-4.43142788808042</v>
+        <v>-3.400583596971079</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.519747807345738</v>
       </c>
       <c r="E92">
-        <v>-28.22029733163732</v>
+        <v>-27.62129796074672</v>
       </c>
       <c r="F92">
-        <v>-5.69755688347344</v>
+        <v>-5.290183378256781</v>
       </c>
       <c r="G92">
-        <v>-4.868045807618279</v>
+        <v>-4.341010268311845</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.613710249573281</v>
       </c>
       <c r="E93">
-        <v>-30.42097267430083</v>
+        <v>-29.5635378202665</v>
       </c>
       <c r="F93">
-        <v>-5.92314153777455</v>
+        <v>-5.165432487738744</v>
       </c>
       <c r="G93">
-        <v>-4.797796031274944</v>
+        <v>-3.91364201301071</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.702675829900917</v>
       </c>
       <c r="E94">
-        <v>-32.60003587476274</v>
+        <v>-31.95266787299623</v>
       </c>
       <c r="F94">
-        <v>-5.625662969736151</v>
+        <v>-5.144665352069586</v>
       </c>
       <c r="G94">
-        <v>-5.186017085574198</v>
+        <v>-3.956503646107654</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.786320007693337</v>
       </c>
       <c r="E95">
-        <v>-34.18790226504928</v>
+        <v>-33.36531175426697</v>
       </c>
       <c r="F95">
-        <v>-5.64545375070844</v>
+        <v>-4.919165426034952</v>
       </c>
       <c r="G95">
-        <v>-5.139689311297637</v>
+        <v>-4.822628433365018</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.868886052015061</v>
       </c>
       <c r="E96">
-        <v>-36.69095740262697</v>
+        <v>-36.43727228871727</v>
       </c>
       <c r="F96">
-        <v>-5.18288017580914</v>
+        <v>-5.248854988687474</v>
       </c>
       <c r="G96">
-        <v>-5.382845570611567</v>
+        <v>-4.850321146801021</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.950579684514525</v>
       </c>
       <c r="E97">
-        <v>-38.57085828895716</v>
+        <v>-39.00296301453206</v>
       </c>
       <c r="F97">
-        <v>-5.344864784252117</v>
+        <v>-4.603979442156024</v>
       </c>
       <c r="G97">
-        <v>-5.592201159969537</v>
+        <v>-5.552981126965792</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.050626095790054</v>
       </c>
       <c r="E98">
-        <v>-41.9640121635865</v>
+        <v>-39.60821167955324</v>
       </c>
       <c r="F98">
-        <v>-5.128914604887583</v>
+        <v>-5.014241626962443</v>
       </c>
       <c r="G98">
-        <v>-6.515244156683591</v>
+        <v>-6.006807262216782</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.166848172166655</v>
       </c>
       <c r="E99">
-        <v>-45.14287411969888</v>
+        <v>-44.77207813947683</v>
       </c>
       <c r="F99">
-        <v>-5.171143331269818</v>
+        <v>-4.826068857501759</v>
       </c>
       <c r="G99">
-        <v>-6.60059664177708</v>
+        <v>-6.251635347028044</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.332416670261019</v>
       </c>
       <c r="E100">
-        <v>-46.4466376361662</v>
+        <v>-45.68901940620894</v>
       </c>
       <c r="F100">
-        <v>-5.081716209342699</v>
+        <v>-4.493773306765381</v>
       </c>
       <c r="G100">
-        <v>-6.458610654143278</v>
+        <v>-5.932528551952155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.528861042356401</v>
       </c>
       <c r="E101">
-        <v>-48.4913806369681</v>
+        <v>-48.15057787221735</v>
       </c>
       <c r="F101">
-        <v>-5.128036439957471</v>
+        <v>-4.307166822455066</v>
       </c>
       <c r="G101">
-        <v>-7.040293368666461</v>
+        <v>-7.261732449242772</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.823356516640684</v>
       </c>
       <c r="E102">
-        <v>-50.62555533882898</v>
+        <v>-50.53957999555635</v>
       </c>
       <c r="F102">
-        <v>-4.413256114318524</v>
+        <v>-3.593064322947927</v>
       </c>
       <c r="G102">
-        <v>-7.314108590219581</v>
+        <v>-6.854760465009086</v>
       </c>
     </row>
   </sheetData>
